--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$95</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$104</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$96</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -4359,7 +4359,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 37.4, "op_wape_pct": 12.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 2287.97, "rev_act": 2931.56, "op_pred": 153.0, "op_act": 192.54}, {"q": "2025Q4", "rev_pred": 1872.28, "rev_act": 1744.72, "op_pred": 125.2, "op_act": 136.64}, {"q": "2026Q1", "rev_pred": 2953.66, "rev_act": 1746.56, "op_pred": 197.51, "op_act": 168.58}, {"q": "2026Q2", "rev_pred": 2764.0, "rev_act": 1704.84, "op_pred": 184.83, "op_act": 193.44}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 37.4, "op_wape_pct": 12.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 2287.97, "rev_act": 2931.56, "op_pred": 153.0, "op_act": 192.54}, {"q": "2025Q4", "rev_pred": 1872.28, "rev_act": 1744.72, "op_pred": 125.2, "op_act": 136.64}, {"q": "2026Q1", "rev_pred": 2953.66, "rev_act": 1746.56, "op_pred": 197.51, "op_act": 168.58}, {"q": "2026Q2", "rev_pred": 2764.0, "rev_act": 1704.84, "op_pred": 184.83, "op_act": 193.44}]}</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO95"/>
+  <dimension ref="A1:AO104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16860,78 +16860,33 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>109667.02</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="18" t="n">
-        <v>50479.39</v>
-      </c>
-      <c r="H78" s="18" t="n">
-        <v>-14215.49</v>
-      </c>
-      <c r="I78" s="18" t="n">
-        <v>-29519.19</v>
-      </c>
-      <c r="J78" s="18" t="n">
-        <v>61845.53</v>
-      </c>
-      <c r="K78" s="34" t="n">
-        <v>68590.24000000001</v>
-      </c>
-      <c r="L78" s="18" t="n">
-        <v>-54654.15</v>
-      </c>
-      <c r="M78" s="18" t="n">
-        <v>-74651.11</v>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>-810.9</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>-8086.96</v>
-      </c>
-      <c r="P78" s="34" t="n">
-        <v>-138203.12</v>
-      </c>
-      <c r="Q78" s="18" t="n">
-        <v>10160.89</v>
-      </c>
-      <c r="R78" s="18" t="n">
-        <v>51876.63</v>
-      </c>
-      <c r="S78" s="18" t="n">
-        <v>46189.15</v>
-      </c>
-      <c r="T78" s="18" t="n">
-        <v>27140.66</v>
-      </c>
-      <c r="U78" s="34" t="n">
-        <v>135367.33</v>
-      </c>
+      <c r="K78" s="9" t="n"/>
+      <c r="P78" s="9" t="n"/>
+      <c r="U78" s="9" t="n"/>
       <c r="V78" s="18" t="n">
-        <v>52382.12</v>
+        <v>688.58</v>
       </c>
       <c r="W78" s="18" t="n">
-        <v>46463.12</v>
+        <v>1221.79</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>-115850.39</v>
+        <v>1208.6</v>
       </c>
       <c r="Y78" s="18" t="n">
-        <v>-22763.08</v>
+        <v>13.2</v>
       </c>
       <c r="Z78" s="34" t="n">
-        <v>-39768.23</v>
+        <v>3132.17</v>
       </c>
       <c r="AA78" s="18" t="n">
-        <v>40909.22</v>
+        <v>531.39</v>
       </c>
       <c r="AB78" s="19" t="n">
-        <v>11471.72</v>
+        <v>245.3</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -16953,78 +16908,33 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>-18.04</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="18" t="n">
-        <v>23.92</v>
-      </c>
-      <c r="H79" s="18" t="n">
-        <v>807.88</v>
-      </c>
-      <c r="I79" s="18" t="n">
-        <v>746.95</v>
-      </c>
-      <c r="J79" s="18" t="n">
-        <v>2820.63</v>
-      </c>
-      <c r="K79" s="34" t="n">
-        <v>4399.38</v>
-      </c>
-      <c r="L79" s="18" t="n">
-        <v>1046.13</v>
-      </c>
-      <c r="M79" s="18" t="n">
-        <v>1276.14</v>
-      </c>
-      <c r="N79" s="18" t="n">
-        <v>922.7</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>1629.81</v>
-      </c>
-      <c r="P79" s="34" t="n">
-        <v>4874.78</v>
-      </c>
-      <c r="Q79" s="18" t="n">
-        <v>1307.99</v>
-      </c>
-      <c r="R79" s="18" t="n">
-        <v>756.02</v>
-      </c>
-      <c r="S79" s="18" t="n">
-        <v>1059.3</v>
-      </c>
-      <c r="T79" s="18" t="n">
-        <v>2240.65</v>
-      </c>
-      <c r="U79" s="34" t="n">
-        <v>5363.96</v>
-      </c>
+      <c r="K79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
+      <c r="U79" s="9" t="n"/>
       <c r="V79" s="18" t="n">
-        <v>504.61</v>
+        <v>4729.36</v>
       </c>
       <c r="W79" s="18" t="n">
-        <v>941.35</v>
+        <v>5227.61</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>1555.63</v>
+        <v>3344.62</v>
       </c>
       <c r="Y79" s="18" t="n">
-        <v>262.04</v>
+        <v>-698.1</v>
       </c>
       <c r="Z79" s="34" t="n">
-        <v>3263.63</v>
+        <v>12603.49</v>
       </c>
       <c r="AA79" s="18" t="n">
-        <v>353.1</v>
+        <v>1156.46</v>
       </c>
       <c r="AB79" s="19" t="n">
-        <v>293.11</v>
+        <v>1219.55</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -17046,56 +16956,33 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>-3319.43</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="18" t="n">
-        <v>-2855.98</v>
-      </c>
-      <c r="H80" s="18" t="n">
-        <v>-2909.45</v>
-      </c>
-      <c r="I80" s="18" t="n">
-        <v>-2799.57</v>
-      </c>
-      <c r="J80" s="18" t="n">
-        <v>-2359.92</v>
-      </c>
-      <c r="K80" s="34" t="n">
-        <v>-10924.92</v>
-      </c>
-      <c r="L80" s="18" t="n">
-        <v>-1442.42</v>
-      </c>
-      <c r="M80" s="18" t="n">
-        <v>-1872.68</v>
-      </c>
+      <c r="K80" s="9" t="n"/>
       <c r="P80" s="9" t="n"/>
       <c r="U80" s="9" t="n"/>
       <c r="V80" s="18" t="n">
-        <v>-2303.75</v>
+        <v>7.55</v>
       </c>
       <c r="W80" s="18" t="n">
-        <v>-2688.09</v>
+        <v>41.3</v>
       </c>
       <c r="X80" s="18" t="n">
-        <v>-3220.76</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Y80" s="18" t="n">
-        <v>-2384.12</v>
+        <v>105.59</v>
       </c>
       <c r="Z80" s="34" t="n">
-        <v>-10596.72</v>
+        <v>227.34</v>
       </c>
       <c r="AA80" s="18" t="n">
-        <v>-2445.21</v>
+        <v>44.56</v>
       </c>
       <c r="AB80" s="19" t="n">
-        <v>-2491.07</v>
+        <v>2.99</v>
       </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
@@ -17117,50 +17004,34 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>0</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="34" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="N81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="K81" s="9" t="n"/>
       <c r="P81" s="9" t="n"/>
-      <c r="S81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="U81" s="9" t="n"/>
+      <c r="V81" s="18" t="n">
+        <v>99.62</v>
+      </c>
+      <c r="W81" s="18" t="n">
+        <v>0.8100000000000001</v>
+      </c>
       <c r="X81" s="18" t="n">
-        <v>0</v>
+        <v>355.32</v>
       </c>
       <c r="Y81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z81" s="9" t="n"/>
-      <c r="AB81" s="5" t="n"/>
+        <v>18.56</v>
+      </c>
+      <c r="Z81" s="34" t="n">
+        <v>474.31</v>
+      </c>
+      <c r="AA81" s="18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB81" s="19" t="n">
+        <v>26.99</v>
+      </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="11" t="n"/>
@@ -17181,78 +17052,33 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>-1.07</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="18" t="n">
-        <v>-8712.58</v>
-      </c>
-      <c r="H82" s="18" t="n">
-        <v>-1082.93</v>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>-3876.62</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>-494.99</v>
-      </c>
-      <c r="K82" s="34" t="n">
-        <v>-14167.12</v>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>3600.27</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>-1005.48</v>
-      </c>
-      <c r="N82" s="18" t="n">
-        <v>-3613.12</v>
-      </c>
-      <c r="O82" s="18" t="n">
-        <v>1475.75</v>
-      </c>
-      <c r="P82" s="34" t="n">
-        <v>457.42</v>
-      </c>
-      <c r="Q82" s="18" t="n">
-        <v>-10901.66</v>
-      </c>
-      <c r="R82" s="18" t="n">
-        <v>-1547.68</v>
-      </c>
-      <c r="S82" s="18" t="n">
-        <v>-578.3</v>
-      </c>
-      <c r="T82" s="18" t="n">
-        <v>-707.48</v>
-      </c>
-      <c r="U82" s="34" t="n">
-        <v>-13735.12</v>
-      </c>
+      <c r="K82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
+      <c r="U82" s="9" t="n"/>
       <c r="V82" s="18" t="n">
-        <v>-91.7</v>
+        <v>150.42</v>
       </c>
       <c r="W82" s="18" t="n">
-        <v>-210.48</v>
+        <v>-150.42</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>-5968.23</v>
+        <v>28.99</v>
       </c>
       <c r="Y82" s="18" t="n">
-        <v>-44.38</v>
+        <v>7.82</v>
       </c>
       <c r="Z82" s="34" t="n">
-        <v>-6314.79</v>
+        <v>36.81</v>
       </c>
       <c r="AA82" s="18" t="n">
-        <v>-5010.02</v>
+        <v>220.25</v>
       </c>
       <c r="AB82" s="19" t="n">
-        <v>-1037</v>
+        <v>74.95</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -17274,78 +17100,33 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>-5954.87</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="G83" s="18" t="n">
-        <v>-62731.04</v>
-      </c>
-      <c r="H83" s="18" t="n">
-        <v>12913.48</v>
-      </c>
-      <c r="I83" s="18" t="n">
-        <v>-351955.98</v>
-      </c>
-      <c r="J83" s="18" t="n">
-        <v>70693.25999999999</v>
-      </c>
-      <c r="K83" s="34" t="n">
-        <v>-331080.28</v>
-      </c>
-      <c r="L83" s="18" t="n">
-        <v>59447.01</v>
-      </c>
-      <c r="M83" s="18" t="n">
-        <v>38092.13</v>
-      </c>
-      <c r="N83" s="18" t="n">
-        <v>-27759.22</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>-43040.19</v>
-      </c>
-      <c r="P83" s="34" t="n">
-        <v>26739.73</v>
-      </c>
-      <c r="Q83" s="18" t="n">
-        <v>-13325.32</v>
-      </c>
-      <c r="R83" s="18" t="n">
-        <v>-6638.85</v>
-      </c>
-      <c r="S83" s="18" t="n">
-        <v>-42134.45</v>
-      </c>
-      <c r="T83" s="18" t="n">
-        <v>-45777.17</v>
-      </c>
-      <c r="U83" s="34" t="n">
-        <v>-107875.79</v>
-      </c>
+      <c r="K83" s="9" t="n"/>
+      <c r="P83" s="9" t="n"/>
+      <c r="U83" s="9" t="n"/>
       <c r="V83" s="18" t="n">
-        <v>-31933.43</v>
+        <v>9.66</v>
       </c>
       <c r="W83" s="18" t="n">
-        <v>-81340.89</v>
+        <v>770.5</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>85768.94</v>
+        <v>-634.73</v>
       </c>
       <c r="Y83" s="18" t="n">
-        <v>-8279.35</v>
+        <v>-55.04</v>
       </c>
       <c r="Z83" s="34" t="n">
-        <v>-35784.73</v>
+        <v>90.39</v>
       </c>
       <c r="AA83" s="18" t="n">
-        <v>-23710.95</v>
+        <v>3642</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>-11528.62</v>
+        <v>1407.72</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -17367,70 +17148,33 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="n">
-        <v>0</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="I84" s="18" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="J84" s="18" t="n">
-        <v>183.87</v>
-      </c>
       <c r="K84" s="9" t="n"/>
-      <c r="L84" s="18" t="n">
-        <v>657.8</v>
-      </c>
-      <c r="M84" s="18" t="n">
-        <v>121.81</v>
-      </c>
-      <c r="N84" s="18" t="n">
-        <v>497.73</v>
-      </c>
-      <c r="O84" s="18" t="n">
-        <v>75.25</v>
-      </c>
-      <c r="P84" s="34" t="n">
-        <v>1352.59</v>
-      </c>
-      <c r="Q84" s="18" t="n">
-        <v>212.35</v>
-      </c>
-      <c r="R84" s="18" t="n">
-        <v>49.69</v>
-      </c>
-      <c r="S84" s="18" t="n">
-        <v>66.52</v>
-      </c>
-      <c r="T84" s="18" t="n">
-        <v>17.87</v>
-      </c>
-      <c r="U84" s="34" t="n">
-        <v>346.43</v>
-      </c>
+      <c r="P84" s="9" t="n"/>
+      <c r="U84" s="9" t="n"/>
       <c r="V84" s="18" t="n">
-        <v>13.66</v>
+        <v>27.91</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>0</v>
+        <v>24067.42</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>11.04</v>
+        <v>-8550.540000000001</v>
       </c>
       <c r="Y84" s="18" t="n">
-        <v>233.1</v>
+        <v>-4468.24</v>
       </c>
       <c r="Z84" s="34" t="n">
-        <v>257.8</v>
+        <v>11076.55</v>
       </c>
       <c r="AA84" s="18" t="n">
-        <v>2.79</v>
+        <v>3564.22</v>
       </c>
       <c r="AB84" s="19" t="n">
-        <v>29.75</v>
+        <v>1912.26</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -17452,78 +17196,33 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>2208.22</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="18" t="n">
-        <v>1621.17</v>
-      </c>
-      <c r="H85" s="18" t="n">
-        <v>7303.58</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>2215.62</v>
-      </c>
-      <c r="J85" s="18" t="n">
-        <v>104988.88</v>
-      </c>
-      <c r="K85" s="34" t="n">
-        <v>116129.25</v>
-      </c>
-      <c r="L85" s="18" t="n">
-        <v>18328.53</v>
-      </c>
-      <c r="M85" s="18" t="n">
-        <v>22623.63</v>
-      </c>
-      <c r="N85" s="18" t="n">
-        <v>24593.62</v>
-      </c>
-      <c r="O85" s="18" t="n">
-        <v>45279.4</v>
-      </c>
-      <c r="P85" s="34" t="n">
-        <v>110825.18</v>
-      </c>
-      <c r="Q85" s="18" t="n">
-        <v>28887.93</v>
-      </c>
-      <c r="R85" s="18" t="n">
-        <v>34845.71</v>
-      </c>
-      <c r="S85" s="18" t="n">
-        <v>47319.67</v>
-      </c>
-      <c r="T85" s="18" t="n">
-        <v>40349.99</v>
-      </c>
-      <c r="U85" s="34" t="n">
-        <v>151403.3</v>
-      </c>
+      <c r="K85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
+      <c r="U85" s="9" t="n"/>
       <c r="V85" s="18" t="n">
-        <v>31875.35</v>
+        <v>1333.85</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>11631.93</v>
+        <v>-1008.96</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>4757.89</v>
+        <v>403.14</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>10389.96</v>
+        <v>1244.24</v>
       </c>
       <c r="Z85" s="34" t="n">
-        <v>58655.13</v>
+        <v>1972.27</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>23670.68</v>
+        <v>6841.73</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>11228.93</v>
+        <v>2975.39</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -17545,78 +17244,33 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>2182.76</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="G86" s="18" t="n">
-        <v>1921</v>
-      </c>
-      <c r="H86" s="18" t="n">
-        <v>7224.49</v>
-      </c>
-      <c r="I86" s="18" t="n">
-        <v>2341.65</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>107127.96</v>
-      </c>
-      <c r="K86" s="34" t="n">
-        <v>118615.1</v>
-      </c>
-      <c r="L86" s="18" t="n">
-        <v>18904.49</v>
-      </c>
-      <c r="M86" s="18" t="n">
-        <v>22584.45</v>
-      </c>
-      <c r="N86" s="18" t="n">
-        <v>25382.05</v>
-      </c>
-      <c r="O86" s="18" t="n">
-        <v>45451.78</v>
-      </c>
-      <c r="P86" s="34" t="n">
-        <v>112322.77</v>
-      </c>
-      <c r="Q86" s="18" t="n">
-        <v>28905.72</v>
-      </c>
-      <c r="R86" s="18" t="n">
-        <v>34895.24</v>
-      </c>
-      <c r="S86" s="18" t="n">
-        <v>47373.29</v>
-      </c>
-      <c r="T86" s="18" t="n">
-        <v>40471.18</v>
-      </c>
-      <c r="U86" s="34" t="n">
-        <v>151645.43</v>
-      </c>
+      <c r="K86" s="9" t="n"/>
+      <c r="P86" s="9" t="n"/>
+      <c r="U86" s="9" t="n"/>
       <c r="V86" s="18" t="n">
-        <v>31950.15</v>
+        <v>-4040.78</v>
       </c>
       <c r="W86" s="18" t="n">
-        <v>11635.28</v>
+        <v>-4005.82</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>5309.22</v>
+        <v>-2136.02</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>10676.87</v>
+        <v>711.3</v>
       </c>
       <c r="Z86" s="34" t="n">
-        <v>59571.52</v>
+        <v>-9471.32</v>
       </c>
       <c r="AA86" s="18" t="n">
-        <v>23705.77</v>
+        <v>-625.0700000000001</v>
       </c>
       <c r="AB86" s="19" t="n">
-        <v>11228.93</v>
+        <v>-974.25</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -17638,78 +17292,78 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E87" s="18" t="n">
-        <v>-18440.05</v>
+        <v>109667.02</v>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="18" t="n">
-        <v>-14760.37</v>
+        <v>50479.39</v>
       </c>
       <c r="H87" s="18" t="n">
-        <v>-10177.3</v>
+        <v>-14215.49</v>
       </c>
       <c r="I87" s="18" t="n">
-        <v>455157.1</v>
+        <v>-29519.19</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>-177498.13</v>
+        <v>61845.53</v>
       </c>
       <c r="K87" s="34" t="n">
-        <v>252721.3</v>
+        <v>68590.24000000001</v>
       </c>
       <c r="L87" s="18" t="n">
-        <v>-2397.96</v>
+        <v>-54654.15</v>
       </c>
       <c r="M87" s="18" t="n">
-        <v>26115.43</v>
+        <v>-74651.11</v>
       </c>
       <c r="N87" s="18" t="n">
-        <v>25748.45</v>
+        <v>-810.9</v>
       </c>
       <c r="O87" s="18" t="n">
-        <v>20850.79</v>
+        <v>-8086.96</v>
       </c>
       <c r="P87" s="34" t="n">
-        <v>70316.71000000001</v>
+        <v>-138203.12</v>
       </c>
       <c r="Q87" s="18" t="n">
-        <v>36366.38</v>
+        <v>10160.89</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>-37953.64</v>
+        <v>51876.63</v>
       </c>
       <c r="S87" s="18" t="n">
-        <v>-16047.62</v>
+        <v>46189.15</v>
       </c>
       <c r="T87" s="18" t="n">
-        <v>16108.79</v>
+        <v>27140.66</v>
       </c>
       <c r="U87" s="34" t="n">
-        <v>-1526.09</v>
+        <v>135367.33</v>
       </c>
       <c r="V87" s="18" t="n">
-        <v>38601.9</v>
+        <v>52382.12</v>
       </c>
       <c r="W87" s="18" t="n">
-        <v>-3382.47</v>
+        <v>46463.12</v>
       </c>
       <c r="X87" s="18" t="n">
-        <v>-9104.67</v>
+        <v>-115850.39</v>
       </c>
       <c r="Y87" s="18" t="n">
-        <v>1562.48</v>
+        <v>-22763.08</v>
       </c>
       <c r="Z87" s="34" t="n">
-        <v>27677.24</v>
+        <v>-39768.23</v>
       </c>
       <c r="AA87" s="18" t="n">
-        <v>-18125.21</v>
+        <v>40909.22</v>
       </c>
       <c r="AB87" s="19" t="n">
-        <v>18010.87</v>
+        <v>11471.72</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -17731,70 +17385,78 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>차입금의증가</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>16611.76</v>
+        <v>-18.04</v>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="18" t="n">
-        <v>16917.18</v>
+        <v>23.92</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>27542.48</v>
+        <v>807.88</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>8678.5</v>
+        <v>746.95</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>16388.34</v>
+        <v>2820.63</v>
       </c>
       <c r="K88" s="34" t="n">
-        <v>69526.5</v>
+        <v>4399.38</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>22242.5</v>
+        <v>1046.13</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>81918.46000000001</v>
-      </c>
-      <c r="P88" s="9" t="n"/>
+        <v>1276.14</v>
+      </c>
+      <c r="N88" s="18" t="n">
+        <v>922.7</v>
+      </c>
+      <c r="O88" s="18" t="n">
+        <v>1629.81</v>
+      </c>
+      <c r="P88" s="34" t="n">
+        <v>4874.78</v>
+      </c>
       <c r="Q88" s="18" t="n">
-        <v>110397.4</v>
+        <v>1307.99</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>3325.62</v>
+        <v>756.02</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>16141.89</v>
+        <v>1059.3</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>62247.56</v>
+        <v>2240.65</v>
       </c>
       <c r="U88" s="34" t="n">
-        <v>192112.47</v>
+        <v>5363.96</v>
       </c>
       <c r="V88" s="18" t="n">
-        <v>57960</v>
+        <v>504.61</v>
       </c>
       <c r="W88" s="18" t="n">
-        <v>1940</v>
+        <v>941.35</v>
       </c>
       <c r="X88" s="18" t="n">
-        <v>8000</v>
+        <v>1555.63</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>3500</v>
+        <v>262.04</v>
       </c>
       <c r="Z88" s="34" t="n">
-        <v>71400</v>
+        <v>3263.63</v>
       </c>
       <c r="AA88" s="18" t="n">
-        <v>10450</v>
+        <v>353.1</v>
       </c>
       <c r="AB88" s="19" t="n">
-        <v>69390</v>
+        <v>293.11</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -17816,78 +17478,56 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>차입금의감소</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>34392.43</v>
+        <v>-3319.43</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="18" t="n">
-        <v>30975.25</v>
+        <v>-2855.98</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>37009.47</v>
+        <v>-2909.45</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>11668</v>
+        <v>-2799.57</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>151690.86</v>
+        <v>-2359.92</v>
       </c>
       <c r="K89" s="34" t="n">
-        <v>231343.58</v>
+        <v>-10924.92</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>17648.55</v>
+        <v>-1442.42</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>54936.66</v>
-      </c>
-      <c r="N89" s="18" t="n">
-        <v>19013.12</v>
-      </c>
-      <c r="O89" s="18" t="n">
-        <v>25807.76</v>
-      </c>
-      <c r="P89" s="34" t="n">
-        <v>117406.09</v>
-      </c>
-      <c r="Q89" s="18" t="n">
-        <v>69876.17999999999</v>
-      </c>
-      <c r="R89" s="18" t="n">
-        <v>37096.55</v>
-      </c>
-      <c r="S89" s="18" t="n">
-        <v>27626.8</v>
-      </c>
-      <c r="T89" s="18" t="n">
-        <v>35644.54</v>
-      </c>
-      <c r="U89" s="34" t="n">
-        <v>170244.07</v>
-      </c>
+        <v>-1872.68</v>
+      </c>
+      <c r="P89" s="9" t="n"/>
+      <c r="U89" s="9" t="n"/>
       <c r="V89" s="18" t="n">
-        <v>17157.6</v>
+        <v>-2303.75</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>4097.6</v>
+        <v>-2688.09</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>10157.6</v>
+        <v>-3220.76</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>5657.6</v>
+        <v>-2384.12</v>
       </c>
       <c r="Z89" s="34" t="n">
-        <v>37070.4</v>
+        <v>-10596.72</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>27157.6</v>
+        <v>-2445.21</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>49997.6</v>
+        <v>-2491.07</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -17909,74 +17549,50 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>659.38</v>
+        <v>0</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>697.22</v>
+        <v>10.89</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>710.3200000000001</v>
+        <v>0</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>865.21</v>
+        <v>0</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>740.63</v>
+        <v>0</v>
       </c>
       <c r="K90" s="34" t="n">
-        <v>3013.38</v>
-      </c>
-      <c r="L90" s="18" t="n">
-        <v>844.49</v>
-      </c>
-      <c r="M90" s="18" t="n">
-        <v>866.38</v>
+        <v>10.89</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>1183.5</v>
+        <v>0</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>4029.34</v>
-      </c>
-      <c r="P90" s="34" t="n">
-        <v>6923.71</v>
-      </c>
-      <c r="Q90" s="18" t="n">
-        <v>4154.84</v>
-      </c>
-      <c r="R90" s="18" t="n">
-        <v>4182.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P90" s="9" t="n"/>
       <c r="S90" s="18" t="n">
-        <v>4562.73</v>
+        <v>0</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>4259.71</v>
-      </c>
-      <c r="U90" s="34" t="n">
-        <v>17159.98</v>
-      </c>
-      <c r="V90" s="18" t="n">
-        <v>2200.5</v>
-      </c>
-      <c r="W90" s="18" t="n">
-        <v>1215.78</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U90" s="9" t="n"/>
       <c r="X90" s="18" t="n">
-        <v>2464.15</v>
+        <v>0</v>
+      </c>
+      <c r="Y90" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="Z90" s="9" t="n"/>
-      <c r="AA90" s="18" t="n">
-        <v>1417.61</v>
-      </c>
-      <c r="AB90" s="19" t="n">
-        <v>1381.53</v>
-      </c>
+      <c r="AB90" s="5" t="n"/>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
       <c r="AE90" s="11" t="n"/>
@@ -17997,78 +17613,78 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E91" s="18" t="n">
-        <v>170554.29</v>
+        <v>-1.07</v>
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="18" t="n">
-        <v>-54041.49</v>
+        <v>-8712.58</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>-22888.69</v>
+        <v>-1082.93</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>147735.41</v>
+        <v>-3876.62</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>-90836.78999999999</v>
+        <v>-494.99</v>
       </c>
       <c r="K91" s="34" t="n">
-        <v>-20031.56</v>
+        <v>-14167.12</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>4818.53</v>
+        <v>3600.27</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>-20842.58</v>
+        <v>-1005.48</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>-5566.52</v>
+        <v>-3613.12</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>-60987.82</v>
+        <v>1475.75</v>
       </c>
       <c r="P91" s="34" t="n">
-        <v>-82578.39</v>
+        <v>457.42</v>
       </c>
       <c r="Q91" s="18" t="n">
-        <v>66516.81</v>
+        <v>-10901.66</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>14565.13</v>
+        <v>-1547.68</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>-24537.23</v>
+        <v>-578.3</v>
       </c>
       <c r="T91" s="18" t="n">
-        <v>-30434.08</v>
+        <v>-707.48</v>
       </c>
       <c r="U91" s="34" t="n">
-        <v>26110.63</v>
+        <v>-13735.12</v>
       </c>
       <c r="V91" s="18" t="n">
-        <v>59190.87</v>
+        <v>-91.7</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>-39187.59</v>
+        <v>-210.48</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>-38392.41</v>
+        <v>-5968.23</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>-29504.66</v>
+        <v>-44.38</v>
       </c>
       <c r="Z91" s="34" t="n">
-        <v>-47893.79</v>
+        <v>-6314.79</v>
       </c>
       <c r="AA91" s="18" t="n">
-        <v>-919.7</v>
+        <v>-5010.02</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>17949.87</v>
+        <v>-1037</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -18090,78 +17706,78 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E92" s="18" t="n">
-        <v>85282.19</v>
+        <v>-5954.87</v>
       </c>
       <c r="F92" s="9" t="n"/>
       <c r="G92" s="18" t="n">
-        <v>69442.91</v>
+        <v>-62731.04</v>
       </c>
       <c r="H92" s="18" t="n">
-        <v>-11409.38</v>
+        <v>12913.48</v>
       </c>
       <c r="I92" s="18" t="n">
-        <v>74053.47</v>
+        <v>-351955.98</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>-45877.44</v>
+        <v>70693.25999999999</v>
       </c>
       <c r="K92" s="34" t="n">
-        <v>86209.56</v>
+        <v>-331080.28</v>
       </c>
       <c r="L92" s="18" t="n">
-        <v>88633.19</v>
+        <v>59447.01</v>
       </c>
       <c r="M92" s="18" t="n">
-        <v>-10399.04</v>
+        <v>38092.13</v>
       </c>
       <c r="N92" s="18" t="n">
-        <v>-2744.84</v>
+        <v>-27759.22</v>
       </c>
       <c r="O92" s="18" t="n">
-        <v>-30711.45</v>
+        <v>-43040.19</v>
       </c>
       <c r="P92" s="34" t="n">
-        <v>44777.86</v>
+        <v>26739.73</v>
       </c>
       <c r="Q92" s="18" t="n">
-        <v>78092.71000000001</v>
+        <v>-13325.32</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>7280.99</v>
+        <v>-6638.85</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>-12544.29</v>
+        <v>-42134.45</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>-1940.92</v>
+        <v>-45777.17</v>
       </c>
       <c r="U92" s="34" t="n">
-        <v>70888.49000000001</v>
+        <v>-107875.79</v>
       </c>
       <c r="V92" s="18" t="n">
-        <v>130079.36</v>
+        <v>-31933.43</v>
       </c>
       <c r="W92" s="18" t="n">
-        <v>-39187.59</v>
+        <v>-81340.89</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>-38392.41</v>
+        <v>85768.94</v>
       </c>
       <c r="Y92" s="18" t="n">
-        <v>-29504.65</v>
+        <v>-8279.35</v>
       </c>
       <c r="Z92" s="34" t="n">
-        <v>22994.71</v>
+        <v>-35784.73</v>
       </c>
       <c r="AA92" s="18" t="n">
-        <v>22075</v>
+        <v>-23710.95</v>
       </c>
       <c r="AB92" s="19" t="n">
-        <v>17949.88</v>
+        <v>-11528.62</v>
       </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -18183,65 +17799,70 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="9" t="n"/>
-      <c r="G93" s="18" t="n">
-        <v>299.83</v>
-      </c>
       <c r="I93" s="18" t="n">
-        <v>126.03</v>
+        <v>14.67</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>2139.08</v>
+        <v>183.87</v>
       </c>
       <c r="K93" s="9" t="n"/>
       <c r="L93" s="18" t="n">
-        <v>575.96</v>
+        <v>657.8</v>
+      </c>
+      <c r="M93" s="18" t="n">
+        <v>121.81</v>
       </c>
       <c r="N93" s="18" t="n">
-        <v>788.4299999999999</v>
+        <v>497.73</v>
       </c>
       <c r="O93" s="18" t="n">
-        <v>172.38</v>
-      </c>
-      <c r="P93" s="9" t="n"/>
+        <v>75.25</v>
+      </c>
+      <c r="P93" s="34" t="n">
+        <v>1352.59</v>
+      </c>
       <c r="Q93" s="18" t="n">
-        <v>17.79</v>
+        <v>212.35</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>49.53</v>
+        <v>49.69</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>53.62</v>
+        <v>66.52</v>
       </c>
       <c r="T93" s="18" t="n">
-        <v>121.19</v>
+        <v>17.87</v>
       </c>
       <c r="U93" s="34" t="n">
-        <v>242.13</v>
+        <v>346.43</v>
       </c>
       <c r="V93" s="18" t="n">
-        <v>74.8</v>
+        <v>13.66</v>
       </c>
       <c r="W93" s="18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>551.33</v>
+        <v>11.04</v>
       </c>
       <c r="Y93" s="18" t="n">
-        <v>286.91</v>
+        <v>233.1</v>
       </c>
       <c r="Z93" s="34" t="n">
-        <v>916.39</v>
+        <v>257.8</v>
       </c>
       <c r="AA93" s="18" t="n">
-        <v>35.09</v>
+        <v>2.79</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>0</v>
+        <v>29.75</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -18263,30 +17884,79 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>2208.22</v>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="K94" s="9" t="n"/>
+      <c r="G94" s="18" t="n">
+        <v>1621.17</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>7303.58</v>
+      </c>
+      <c r="I94" s="18" t="n">
+        <v>2215.62</v>
+      </c>
+      <c r="J94" s="18" t="n">
+        <v>104988.88</v>
+      </c>
+      <c r="K94" s="34" t="n">
+        <v>116129.25</v>
+      </c>
+      <c r="L94" s="18" t="n">
+        <v>18328.53</v>
+      </c>
+      <c r="M94" s="18" t="n">
+        <v>22623.63</v>
+      </c>
+      <c r="N94" s="18" t="n">
+        <v>24593.62</v>
+      </c>
       <c r="O94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" s="9" t="n"/>
+        <v>45279.4</v>
+      </c>
+      <c r="P94" s="34" t="n">
+        <v>110825.18</v>
+      </c>
+      <c r="Q94" s="18" t="n">
+        <v>28887.93</v>
+      </c>
+      <c r="R94" s="18" t="n">
+        <v>34845.71</v>
+      </c>
       <c r="S94" s="18" t="n">
-        <v>0</v>
+        <v>47319.67</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" s="9" t="n"/>
+        <v>40349.99</v>
+      </c>
+      <c r="U94" s="34" t="n">
+        <v>151403.3</v>
+      </c>
+      <c r="V94" s="18" t="n">
+        <v>31875.35</v>
+      </c>
+      <c r="W94" s="18" t="n">
+        <v>11631.93</v>
+      </c>
       <c r="X94" s="18" t="n">
-        <v>827.97</v>
+        <v>4757.89</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="9" t="n"/>
-      <c r="AB94" s="5" t="n"/>
+        <v>10389.96</v>
+      </c>
+      <c r="Z94" s="34" t="n">
+        <v>58655.13</v>
+      </c>
+      <c r="AA94" s="18" t="n">
+        <v>23670.68</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>11228.93</v>
+      </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
       <c r="AE94" s="11" t="n"/>
@@ -18307,18 +17977,79 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>사채의감소</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>2182.76</v>
       </c>
       <c r="F95" s="9" t="n"/>
-      <c r="K95" s="9" t="n"/>
+      <c r="G95" s="18" t="n">
+        <v>1921</v>
+      </c>
+      <c r="H95" s="18" t="n">
+        <v>7224.49</v>
+      </c>
+      <c r="I95" s="18" t="n">
+        <v>2341.65</v>
+      </c>
+      <c r="J95" s="18" t="n">
+        <v>107127.96</v>
+      </c>
+      <c r="K95" s="34" t="n">
+        <v>118615.1</v>
+      </c>
+      <c r="L95" s="18" t="n">
+        <v>18904.49</v>
+      </c>
+      <c r="M95" s="18" t="n">
+        <v>22584.45</v>
+      </c>
+      <c r="N95" s="18" t="n">
+        <v>25382.05</v>
+      </c>
       <c r="O95" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="9" t="n"/>
-      <c r="U95" s="9" t="n"/>
-      <c r="Z95" s="9" t="n"/>
-      <c r="AB95" s="5" t="n"/>
+        <v>45451.78</v>
+      </c>
+      <c r="P95" s="34" t="n">
+        <v>112322.77</v>
+      </c>
+      <c r="Q95" s="18" t="n">
+        <v>28905.72</v>
+      </c>
+      <c r="R95" s="18" t="n">
+        <v>34895.24</v>
+      </c>
+      <c r="S95" s="18" t="n">
+        <v>47373.29</v>
+      </c>
+      <c r="T95" s="18" t="n">
+        <v>40471.18</v>
+      </c>
+      <c r="U95" s="34" t="n">
+        <v>151645.43</v>
+      </c>
+      <c r="V95" s="18" t="n">
+        <v>31950.15</v>
+      </c>
+      <c r="W95" s="18" t="n">
+        <v>11635.28</v>
+      </c>
+      <c r="X95" s="18" t="n">
+        <v>5309.22</v>
+      </c>
+      <c r="Y95" s="18" t="n">
+        <v>10676.87</v>
+      </c>
+      <c r="Z95" s="34" t="n">
+        <v>59571.52</v>
+      </c>
+      <c r="AA95" s="18" t="n">
+        <v>23705.77</v>
+      </c>
+      <c r="AB95" s="19" t="n">
+        <v>11228.93</v>
+      </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
       <c r="AE95" s="11" t="n"/>
@@ -18332,6 +18063,707 @@
       <c r="AM95" s="10" t="n"/>
       <c r="AN95" s="10" t="n"/>
       <c r="AO95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>-18440.05</v>
+      </c>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="18" t="n">
+        <v>-14760.37</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>-10177.3</v>
+      </c>
+      <c r="I96" s="18" t="n">
+        <v>455157.1</v>
+      </c>
+      <c r="J96" s="18" t="n">
+        <v>-177498.13</v>
+      </c>
+      <c r="K96" s="34" t="n">
+        <v>252721.3</v>
+      </c>
+      <c r="L96" s="18" t="n">
+        <v>-2397.96</v>
+      </c>
+      <c r="M96" s="18" t="n">
+        <v>26115.43</v>
+      </c>
+      <c r="N96" s="18" t="n">
+        <v>25748.45</v>
+      </c>
+      <c r="O96" s="18" t="n">
+        <v>20850.79</v>
+      </c>
+      <c r="P96" s="34" t="n">
+        <v>70316.71000000001</v>
+      </c>
+      <c r="Q96" s="18" t="n">
+        <v>36366.38</v>
+      </c>
+      <c r="R96" s="18" t="n">
+        <v>-37953.64</v>
+      </c>
+      <c r="S96" s="18" t="n">
+        <v>-16047.62</v>
+      </c>
+      <c r="T96" s="18" t="n">
+        <v>16108.79</v>
+      </c>
+      <c r="U96" s="34" t="n">
+        <v>-1526.09</v>
+      </c>
+      <c r="V96" s="18" t="n">
+        <v>38601.9</v>
+      </c>
+      <c r="W96" s="18" t="n">
+        <v>-3382.47</v>
+      </c>
+      <c r="X96" s="18" t="n">
+        <v>-9104.67</v>
+      </c>
+      <c r="Y96" s="18" t="n">
+        <v>1562.48</v>
+      </c>
+      <c r="Z96" s="34" t="n">
+        <v>27677.24</v>
+      </c>
+      <c r="AA96" s="18" t="n">
+        <v>-18125.21</v>
+      </c>
+      <c r="AB96" s="19" t="n">
+        <v>18010.87</v>
+      </c>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="10" t="n"/>
+      <c r="AL96" s="10" t="n"/>
+      <c r="AM96" s="10" t="n"/>
+      <c r="AN96" s="10" t="n"/>
+      <c r="AO96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>차입금의증가</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>16611.76</v>
+      </c>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="18" t="n">
+        <v>16917.18</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>27542.48</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>8678.5</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>16388.34</v>
+      </c>
+      <c r="K97" s="34" t="n">
+        <v>69526.5</v>
+      </c>
+      <c r="L97" s="18" t="n">
+        <v>22242.5</v>
+      </c>
+      <c r="M97" s="18" t="n">
+        <v>81918.46000000001</v>
+      </c>
+      <c r="P97" s="9" t="n"/>
+      <c r="Q97" s="18" t="n">
+        <v>110397.4</v>
+      </c>
+      <c r="R97" s="18" t="n">
+        <v>3325.62</v>
+      </c>
+      <c r="S97" s="18" t="n">
+        <v>16141.89</v>
+      </c>
+      <c r="T97" s="18" t="n">
+        <v>62247.56</v>
+      </c>
+      <c r="U97" s="34" t="n">
+        <v>192112.47</v>
+      </c>
+      <c r="V97" s="18" t="n">
+        <v>57960</v>
+      </c>
+      <c r="W97" s="18" t="n">
+        <v>1940</v>
+      </c>
+      <c r="X97" s="18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y97" s="18" t="n">
+        <v>3500</v>
+      </c>
+      <c r="Z97" s="34" t="n">
+        <v>71400</v>
+      </c>
+      <c r="AA97" s="18" t="n">
+        <v>10450</v>
+      </c>
+      <c r="AB97" s="19" t="n">
+        <v>69390</v>
+      </c>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="11" t="n"/>
+      <c r="AK97" s="10" t="n"/>
+      <c r="AL97" s="10" t="n"/>
+      <c r="AM97" s="10" t="n"/>
+      <c r="AN97" s="10" t="n"/>
+      <c r="AO97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>차입금의감소</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>34392.43</v>
+      </c>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="18" t="n">
+        <v>30975.25</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>37009.47</v>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>11668</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>151690.86</v>
+      </c>
+      <c r="K98" s="34" t="n">
+        <v>231343.58</v>
+      </c>
+      <c r="L98" s="18" t="n">
+        <v>17648.55</v>
+      </c>
+      <c r="M98" s="18" t="n">
+        <v>54936.66</v>
+      </c>
+      <c r="N98" s="18" t="n">
+        <v>19013.12</v>
+      </c>
+      <c r="O98" s="18" t="n">
+        <v>25807.76</v>
+      </c>
+      <c r="P98" s="34" t="n">
+        <v>117406.09</v>
+      </c>
+      <c r="Q98" s="18" t="n">
+        <v>69876.17999999999</v>
+      </c>
+      <c r="R98" s="18" t="n">
+        <v>37096.55</v>
+      </c>
+      <c r="S98" s="18" t="n">
+        <v>27626.8</v>
+      </c>
+      <c r="T98" s="18" t="n">
+        <v>35644.54</v>
+      </c>
+      <c r="U98" s="34" t="n">
+        <v>170244.07</v>
+      </c>
+      <c r="V98" s="18" t="n">
+        <v>17157.6</v>
+      </c>
+      <c r="W98" s="18" t="n">
+        <v>4097.6</v>
+      </c>
+      <c r="X98" s="18" t="n">
+        <v>10157.6</v>
+      </c>
+      <c r="Y98" s="18" t="n">
+        <v>5657.6</v>
+      </c>
+      <c r="Z98" s="34" t="n">
+        <v>37070.4</v>
+      </c>
+      <c r="AA98" s="18" t="n">
+        <v>27157.6</v>
+      </c>
+      <c r="AB98" s="19" t="n">
+        <v>49997.6</v>
+      </c>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="10" t="n"/>
+      <c r="AL98" s="10" t="n"/>
+      <c r="AM98" s="10" t="n"/>
+      <c r="AN98" s="10" t="n"/>
+      <c r="AO98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>659.38</v>
+      </c>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="18" t="n">
+        <v>697.22</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>710.3200000000001</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>865.21</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>740.63</v>
+      </c>
+      <c r="K99" s="34" t="n">
+        <v>3013.38</v>
+      </c>
+      <c r="L99" s="18" t="n">
+        <v>844.49</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>866.38</v>
+      </c>
+      <c r="N99" s="18" t="n">
+        <v>1183.5</v>
+      </c>
+      <c r="O99" s="18" t="n">
+        <v>4029.34</v>
+      </c>
+      <c r="P99" s="34" t="n">
+        <v>6923.71</v>
+      </c>
+      <c r="Q99" s="18" t="n">
+        <v>4154.84</v>
+      </c>
+      <c r="R99" s="18" t="n">
+        <v>4182.7</v>
+      </c>
+      <c r="S99" s="18" t="n">
+        <v>4562.73</v>
+      </c>
+      <c r="T99" s="18" t="n">
+        <v>4259.71</v>
+      </c>
+      <c r="U99" s="34" t="n">
+        <v>17159.98</v>
+      </c>
+      <c r="V99" s="18" t="n">
+        <v>2200.5</v>
+      </c>
+      <c r="W99" s="18" t="n">
+        <v>1215.78</v>
+      </c>
+      <c r="X99" s="18" t="n">
+        <v>2464.15</v>
+      </c>
+      <c r="Z99" s="9" t="n"/>
+      <c r="AA99" s="18" t="n">
+        <v>1417.61</v>
+      </c>
+      <c r="AB99" s="19" t="n">
+        <v>1381.53</v>
+      </c>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="10" t="n"/>
+      <c r="AL99" s="10" t="n"/>
+      <c r="AM99" s="10" t="n"/>
+      <c r="AN99" s="10" t="n"/>
+      <c r="AO99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>170554.29</v>
+      </c>
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="18" t="n">
+        <v>-54041.49</v>
+      </c>
+      <c r="H100" s="18" t="n">
+        <v>-22888.69</v>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>147735.41</v>
+      </c>
+      <c r="J100" s="18" t="n">
+        <v>-90836.78999999999</v>
+      </c>
+      <c r="K100" s="34" t="n">
+        <v>-20031.56</v>
+      </c>
+      <c r="L100" s="18" t="n">
+        <v>4818.53</v>
+      </c>
+      <c r="M100" s="18" t="n">
+        <v>-20842.58</v>
+      </c>
+      <c r="N100" s="18" t="n">
+        <v>-5566.52</v>
+      </c>
+      <c r="O100" s="18" t="n">
+        <v>-60987.82</v>
+      </c>
+      <c r="P100" s="34" t="n">
+        <v>-82578.39</v>
+      </c>
+      <c r="Q100" s="18" t="n">
+        <v>66516.81</v>
+      </c>
+      <c r="R100" s="18" t="n">
+        <v>14565.13</v>
+      </c>
+      <c r="S100" s="18" t="n">
+        <v>-24537.23</v>
+      </c>
+      <c r="T100" s="18" t="n">
+        <v>-30434.08</v>
+      </c>
+      <c r="U100" s="34" t="n">
+        <v>26110.63</v>
+      </c>
+      <c r="V100" s="18" t="n">
+        <v>59190.87</v>
+      </c>
+      <c r="W100" s="18" t="n">
+        <v>-39187.59</v>
+      </c>
+      <c r="X100" s="18" t="n">
+        <v>-38392.41</v>
+      </c>
+      <c r="Y100" s="18" t="n">
+        <v>-29504.66</v>
+      </c>
+      <c r="Z100" s="34" t="n">
+        <v>-47893.79</v>
+      </c>
+      <c r="AA100" s="18" t="n">
+        <v>-919.7</v>
+      </c>
+      <c r="AB100" s="19" t="n">
+        <v>17949.87</v>
+      </c>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="10" t="n"/>
+      <c r="AL100" s="10" t="n"/>
+      <c r="AM100" s="10" t="n"/>
+      <c r="AN100" s="10" t="n"/>
+      <c r="AO100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>85282.19</v>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="18" t="n">
+        <v>69442.91</v>
+      </c>
+      <c r="H101" s="18" t="n">
+        <v>-11409.38</v>
+      </c>
+      <c r="I101" s="18" t="n">
+        <v>74053.47</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>-45877.44</v>
+      </c>
+      <c r="K101" s="34" t="n">
+        <v>86209.56</v>
+      </c>
+      <c r="L101" s="18" t="n">
+        <v>88633.19</v>
+      </c>
+      <c r="M101" s="18" t="n">
+        <v>-10399.04</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>-2744.84</v>
+      </c>
+      <c r="O101" s="18" t="n">
+        <v>-30711.45</v>
+      </c>
+      <c r="P101" s="34" t="n">
+        <v>44777.86</v>
+      </c>
+      <c r="Q101" s="18" t="n">
+        <v>78092.71000000001</v>
+      </c>
+      <c r="R101" s="18" t="n">
+        <v>7280.99</v>
+      </c>
+      <c r="S101" s="18" t="n">
+        <v>-12544.29</v>
+      </c>
+      <c r="T101" s="18" t="n">
+        <v>-1940.92</v>
+      </c>
+      <c r="U101" s="34" t="n">
+        <v>70888.49000000001</v>
+      </c>
+      <c r="V101" s="18" t="n">
+        <v>130079.36</v>
+      </c>
+      <c r="W101" s="18" t="n">
+        <v>-39187.59</v>
+      </c>
+      <c r="X101" s="18" t="n">
+        <v>-38392.41</v>
+      </c>
+      <c r="Y101" s="18" t="n">
+        <v>-29504.65</v>
+      </c>
+      <c r="Z101" s="34" t="n">
+        <v>22994.71</v>
+      </c>
+      <c r="AA101" s="18" t="n">
+        <v>22075</v>
+      </c>
+      <c r="AB101" s="19" t="n">
+        <v>17949.88</v>
+      </c>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="18" t="n">
+        <v>299.83</v>
+      </c>
+      <c r="I102" s="18" t="n">
+        <v>126.03</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>2139.08</v>
+      </c>
+      <c r="K102" s="9" t="n"/>
+      <c r="L102" s="18" t="n">
+        <v>575.96</v>
+      </c>
+      <c r="N102" s="18" t="n">
+        <v>788.4299999999999</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>172.38</v>
+      </c>
+      <c r="P102" s="9" t="n"/>
+      <c r="Q102" s="18" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="R102" s="18" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>53.62</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>121.19</v>
+      </c>
+      <c r="U102" s="34" t="n">
+        <v>242.13</v>
+      </c>
+      <c r="V102" s="18" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X102" s="18" t="n">
+        <v>551.33</v>
+      </c>
+      <c r="Y102" s="18" t="n">
+        <v>286.91</v>
+      </c>
+      <c r="Z102" s="34" t="n">
+        <v>916.39</v>
+      </c>
+      <c r="AA102" s="18" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="AB102" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>무형자산의감소</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="K103" s="9" t="n"/>
+      <c r="O103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="9" t="n"/>
+      <c r="S103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="9" t="n"/>
+      <c r="X103" s="18" t="n">
+        <v>827.97</v>
+      </c>
+      <c r="Y103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="9" t="n"/>
+      <c r="AB103" s="5" t="n"/>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>사채의감소</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
+      <c r="O104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="9" t="n"/>
+      <c r="U104" s="9" t="n"/>
+      <c r="Z104" s="9" t="n"/>
+      <c r="AB104" s="5" t="n"/>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="10" t="n"/>
+      <c r="AL104" s="10" t="n"/>
+      <c r="AM104" s="10" t="n"/>
+      <c r="AN104" s="10" t="n"/>
+      <c r="AO104" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18592,7 +19024,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4334,7 +4334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5205,35 +5205,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5324,35 +5324,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5443,35 +5443,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5681,35 +5681,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5800,35 +5800,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5919,35 +5919,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6038,35 +6038,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6173,7 +6173,7 @@
         <v>11820</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>12030</v>
+        <v>12750</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6264,7 +6264,7 @@
         <v>20850</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>12120</v>
+        <v>12850</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6446,7 +6446,7 @@
         <v>13376.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>12005</v>
+        <v>12253.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>12030</v>
+        <v>12750</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03230483220224094</v>
+        <v>0.0323048322022405</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03109523150897606</v>
+        <v>0.03109523150897582</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34289,7 +34289,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39422,7 +39422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41562,7 +41562,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.13</v>
+        <v>19.22</v>
       </c>
     </row>
     <row r="32">
@@ -41572,7 +41572,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -4334,7 +4334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5205,35 +5205,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5324,35 +5324,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5443,35 +5443,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5681,35 +5681,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5800,35 +5800,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5919,35 +5919,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6038,35 +6038,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6173,7 +6173,7 @@
         <v>11820</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>12750</v>
+        <v>12390</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6264,7 +6264,7 @@
         <v>20850</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>12850</v>
+        <v>12970</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6446,7 +6446,7 @@
         <v>13376.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>12253.3</v>
+        <v>12322.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9328,11 +9328,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>12750</v>
+        <v>12390</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,970원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,990원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34289,7 +34289,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39422,7 +39422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41562,7 +41562,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19.22</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="32">
@@ -41572,7 +41572,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -4334,7 +4334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -5205,35 +5205,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5324,35 +5324,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5443,35 +5443,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5681,35 +5681,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5800,35 +5800,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5919,35 +5919,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6038,35 +6038,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6173,7 +6173,7 @@
         <v>11820</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>12390</v>
+        <v>12060</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6446,7 +6446,7 @@
         <v>13376.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>12322.5</v>
+        <v>12280</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9328,11 +9328,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>12390</v>
+        <v>12060</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,990원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,810원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -34289,7 +34289,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39422,7 +39422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41562,7 +41562,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.67</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="32">
@@ -41572,7 +41572,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4334,7 +4334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.0323048322022405</v>
+        <v>0.03230483220224094</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03109523150897582</v>
+        <v>0.03109523150897606</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5205,35 +5205,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5324,35 +5324,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5443,35 +5443,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5681,35 +5681,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5800,35 +5800,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5919,35 +5919,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6038,35 +6038,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6173,7 +6173,7 @@
         <v>11820</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>12060</v>
+        <v>12030</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6446,7 +6446,7 @@
         <v>13376.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>12280</v>
+        <v>12274</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9328,11 +9328,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>12060</v>
+        <v>12030</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,810원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,400원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03230483220224094</v>
+        <v>0.0323048322022405</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03109523150897606</v>
+        <v>0.03109523150897582</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.18</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -4334,7 +4334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5205,35 +5205,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5324,35 +5324,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5443,35 +5443,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5681,35 +5681,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5800,35 +5800,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5919,35 +5919,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6038,35 +6038,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -4334,7 +4334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -4334,7 +4334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
         <v>11820</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>12030</v>
+        <v>11490</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6355,7 +6355,7 @@
         <v>11010</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>11650</v>
+        <v>11220</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6446,7 +6446,7 @@
         <v>13376.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>12274</v>
+        <v>12143.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>12030</v>
+        <v>11490</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34289,7 +34289,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39422,7 +39422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41562,7 +41562,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.13</v>
+        <v>17.32</v>
       </c>
     </row>
     <row r="32">
@@ -41572,7 +41572,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -4334,7 +4334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5205,35 +5205,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5324,35 +5324,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5443,35 +5443,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5681,35 +5681,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5800,35 +5800,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5919,35 +5919,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6038,35 +6038,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6173,7 +6173,7 @@
         <v>11820</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>11490</v>
+        <v>11080</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6355,7 +6355,7 @@
         <v>11010</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>11220</v>
+        <v>10720</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6446,7 +6446,7 @@
         <v>13376.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>12143.3</v>
+        <v>11972.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9328,11 +9328,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>11490</v>
+        <v>11080</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,400원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,100원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34289,7 +34289,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39422,7 +39422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41562,7 +41562,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.32</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32">
@@ -41572,7 +41572,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -4334,7 +4334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5205,35 +5205,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5324,35 +5324,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5443,35 +5443,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5681,35 +5681,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5800,35 +5800,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5919,35 +5919,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6038,35 +6038,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6173,7 +6173,7 @@
         <v>11820</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>11080</v>
+        <v>11090</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6446,7 +6446,7 @@
         <v>13376.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>11972.9</v>
+        <v>11867.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9328,11 +9328,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>11080</v>
+        <v>11090</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,440원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34289,7 +34289,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39422,7 +39422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41562,7 +41562,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.7</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -4334,7 +4334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5205,35 +5205,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5324,35 +5324,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5443,35 +5443,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5681,35 +5681,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5800,35 +5800,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5919,35 +5919,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6038,35 +6038,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6173,7 +6173,7 @@
         <v>11820</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>11090</v>
+        <v>10970</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6355,7 +6355,7 @@
         <v>11010</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>10720</v>
+        <v>9960</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6446,7 +6446,7 @@
         <v>13376.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>11867.5</v>
+        <v>11502.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9328,11 +9328,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>11090</v>
+        <v>10970</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,440원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,200원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34289,7 +34289,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39422,7 +39422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41562,7 +41562,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.71</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="32">
@@ -41572,7 +41572,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/100090_model.xlsx
+++ b/argus/kship/models/100090_model.xlsx
@@ -4334,7 +4334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5205,35 +5205,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5324,35 +5324,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5443,35 +5443,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5681,35 +5681,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5800,35 +5800,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5919,35 +5919,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6038,35 +6038,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6173,7 +6173,7 @@
         <v>11820</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>10970</v>
+        <v>9530</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6355,7 +6355,7 @@
         <v>11010</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>9960</v>
+        <v>9500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6446,7 +6446,7 @@
         <v>13376.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>11502.7</v>
+        <v>11051.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9328,11 +9328,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>10970</v>
+        <v>9530</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,200원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,190원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34289,7 +34289,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39422,7 +39422,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41562,7 +41562,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.53</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="32">
@@ -41572,7 +41572,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="33">
